--- a/public/tools/jikkajimai-checklist.xlsx
+++ b/public/tools/jikkajimai-checklist.xlsx
@@ -499,7 +499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>にいがた実家じまい帖／更新 2026-10-03／登録不要・無料・再配布可（出典明記）</t>
+          <t>新潟 実家じまいナビ／更新 2026-10-03／登録不要・無料・再配布可（出典明記）</t>
         </is>
       </c>
     </row>
